--- a/knowledge/RehabMind_KnowledgeDB_v3.8.xlsx
+++ b/knowledge/RehabMind_KnowledgeDB_v3.8.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Region" sheetId="1" r:id="Rf80183e03374423a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_ClinicalItem" sheetId="2" r:id="R769953f1c2564b43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Finding" sheetId="3" r:id="Raba05a8a7e1642e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Intervention" sheetId="4" r:id="Ra5f0bb874c9d40d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_RegionClinicalMap" sheetId="5" r:id="R47ecb995b0284f3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_FindingInterventionMap" sheetId="6" r:id="R3d49f840ec1f4b2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_ContextRule" sheetId="7" r:id="Rbff0b4ffa4954711"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_AssessmentFindingMap" sheetId="8" r:id="Rf1302a792af24344"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Evidence" sheetId="9" r:id="Rf0fa0a7c23744175"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Governance" sheetId="10" r:id="R6639e9f662b24a1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_v3.6_MigrationLog" sheetId="11" r:id="Rff51bef223fa46fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_ContextItemMap" sheetId="12" r:id="R439ab977385b471d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Region" sheetId="1" r:id="Refee373eba4944d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_ClinicalItem" sheetId="2" r:id="R4dfef044a7a04aa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Finding" sheetId="3" r:id="R94bee637a60e4d9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Intervention" sheetId="4" r:id="R838450571b124527"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_RegionClinicalMap" sheetId="5" r:id="Rec64910b94244f3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_FindingInterventionMap" sheetId="6" r:id="R2b688263eb754cdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_ContextRule" sheetId="7" r:id="Re227374b7b0045f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_AssessmentFindingMap" sheetId="8" r:id="R1ae76b1105014392"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Evidence" sheetId="9" r:id="R6fefa6b2a9724be2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Governance" sheetId="10" r:id="Rcc4d9abf513a47c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_v3.6_MigrationLog" sheetId="11" r:id="R31c0925dadbd4347"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_ContextItemMap" sheetId="12" r:id="Re5e278bc052549e0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1084,8 +1084,15 @@
       <x:c r="G7" s="8" t="str">
         <x:v>不自动归因足底筋膜</x:v>
       </x:c>
-      <x:c r="H7" s="144"/>
-      <x:c r="I7" s="144"/>
+      <x:c r="H7" s="144" t="str">
+        <x:v>骨与表浅组织：跟骨底部；足跟脂肪垫
+筋膜与肌群起点：足底腱膜近端；趾短屈肌、拇展肌及小趾展肌起点
+神经邻近：足底神经分支</x:v>
+      </x:c>
+      <x:c r="I7" s="144" t="str">
+        <x:v>https://www.ncbi.nlm.nih.gov/books/NBK539705/
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="8" t="str">
@@ -1109,8 +1116,16 @@
       <x:c r="G8" s="8" t="str">
         <x:v>与舟骨内侧可交叉但不合并</x:v>
       </x:c>
-      <x:c r="H8" s="144"/>
-      <x:c r="I8" s="144"/>
+      <x:c r="H8" s="144" t="str">
+        <x:v>筋膜与表浅肌群：足底腱膜；拇展肌；趾短屈肌
+深层邻近：足底方肌；屈趾肌腱；足内在肌群
+相关肌腱：胫骨后肌腱；腓骨长肌腱
+骨与关节：跟骨至中前足的足弓结构</x:v>
+      </x:c>
+      <x:c r="I8" s="144" t="str">
+        <x:v>https://www.ncbi.nlm.nih.gov/books/NBK539705/
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="8" t="str">
@@ -1134,8 +1149,15 @@
       <x:c r="G9" s="8" t="str">
         <x:v>保持定位而非病名</x:v>
       </x:c>
-      <x:c r="H9" s="144"/>
-      <x:c r="I9" s="144"/>
+      <x:c r="H9" s="144" t="str">
+        <x:v>骨与关节：舟骨；内侧楔骨；邻近中足关节
+肌腱：胫骨后肌腱止点；胫骨前肌腱远端邻近
+足底邻近：拇展肌；足底筋膜与足弓支持组织</x:v>
+      </x:c>
+      <x:c r="I9" s="144" t="str">
+        <x:v>https://www.ncbi.nlm.nih.gov/books/NBK539705/
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="8" t="str">
@@ -1159,8 +1181,15 @@
       <x:c r="G10" s="8" t="str">
         <x:v>骨性风险由安全层处理</x:v>
       </x:c>
-      <x:c r="H10" s="144"/>
-      <x:c r="I10" s="144"/>
+      <x:c r="H10" s="144" t="str">
+        <x:v>骨与关节：第五跖骨基底；骰骨；外侧中足关节
+肌腱：腓骨短肌腱止点；第三腓骨肌腱；腓骨长肌腱走行
+足底邻近：小趾展肌；外侧足底筋膜</x:v>
+      </x:c>
+      <x:c r="I10" s="144" t="str">
+        <x:v>https://www.ncbi.nlm.nih.gov/books/NBK539705/
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="8" t="str">
@@ -1184,8 +1213,16 @@
       <x:c r="G11" s="8" t="str">
         <x:v>避免一次拆得过细</x:v>
       </x:c>
-      <x:c r="H11" s="144"/>
-      <x:c r="I11" s="144"/>
+      <x:c r="H11" s="144" t="str">
+        <x:v>肌腱：趾长伸肌腱；拇长伸肌腱；胫骨前肌腱邻近
+肌群：趾短伸肌；拇短伸肌
+骨与关节：跗骨背侧；跖骨基底；中足关节
+神经与支持组织：深腓神经；伸肌支持组织</x:v>
+      </x:c>
+      <x:c r="I11" s="144" t="str">
+        <x:v>https://www.ncbi.nlm.nih.gov/books/NBK539705/
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="8" t="str">
@@ -1209,8 +1246,15 @@
       <x:c r="G12" s="8" t="str">
         <x:v>跖趾具体射线后续按需要细分</x:v>
       </x:c>
-      <x:c r="H12" s="144"/>
-      <x:c r="I12" s="144"/>
+      <x:c r="H12" s="144" t="str">
+        <x:v>骨与关节：第2–5跖骨头；跖趾关节；近节趾骨
+肌腱与肌群：屈趾肌腱；蚓状肌；骨间肌；趾短屈肌；小趾肌群
+周围组织：跖板；足底脂肪垫；趾间神经</x:v>
+      </x:c>
+      <x:c r="I12" s="144" t="str">
+        <x:v>https://www.ncbi.nlm.nih.gov/books/NBK539705/
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="8" t="str">
@@ -1234,8 +1278,16 @@
       <x:c r="G13" s="8" t="str">
         <x:v>作为跑走推进的重要功能入口</x:v>
       </x:c>
-      <x:c r="H13" s="144"/>
-      <x:c r="I13" s="144"/>
+      <x:c r="H13" s="144" t="str">
+        <x:v>骨与关节：第一跖骨头；拇趾近节趾骨；第一跖趾关节；籽骨
+肌腱：拇长屈肌腱；拇长伸肌腱
+肌群：拇短屈肌；拇展肌；拇收肌；拇短伸肌
+周围组织：跖板；关节囊</x:v>
+      </x:c>
+      <x:c r="I13" s="144" t="str">
+        <x:v>https://www.ncbi.nlm.nih.gov/books/NBK539705/
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="96" customHeight="1">
       <x:c r="A14" s="8" t="str">
@@ -1669,8 +1721,15 @@
       <x:c r="G29" s="6" t="str">
         <x:v>与胫骨前缘骨性区域分开；位置仅决定优先检查，不直接等同前侧间室或肌肉病变</x:v>
       </x:c>
-      <x:c r="H29" s="144"/>
-      <x:c r="I29" s="144"/>
+      <x:c r="H29" s="144" t="str">
+        <x:v>肌肉：胫骨前肌；趾长伸肌；拇长伸肌；第三腓骨肌
+骨与周围组织：胫骨前缘邻近；腓骨前方；小腿前侧筋膜
+神经与血管：深腓神经；胫前血管</x:v>
+      </x:c>
+      <x:c r="I29" s="144" t="str">
+        <x:v>https://anatomy.med.utah.edu/diganat/PT/2014_lecture/L11_leg_knee.pdf
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="6" t="str">
@@ -1694,8 +1753,14 @@
       <x:c r="G30" s="6" t="str">
         <x:v>这是骨性风险入口，不与胫骨前肌区合并；前侧胫骨皮质应力损伤属于高风险位置之一</x:v>
       </x:c>
-      <x:c r="H30" s="144"/>
-      <x:c r="I30" s="144"/>
+      <x:c r="H30" s="144" t="str">
+        <x:v>骨与周围组织：胫骨前缘；骨膜及皮下组织
+邻近肌群：胫骨前肌；前外侧趾长伸肌、拇长伸肌</x:v>
+      </x:c>
+      <x:c r="I30" s="144" t="str">
+        <x:v>https://anatomy.med.utah.edu/diganat/PT/2014_lecture/L11_leg_knee.pdf
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="96" customHeight="1">
       <x:c r="A31" s="6" t="str">
@@ -1720,13 +1785,13 @@
         <x:v>用于区分骨/骨膜样负荷线索与后内侧深层肌肉；不直接等同MTSS或应力性骨折</x:v>
       </x:c>
       <x:c r="H31" s="144" t="str">
-        <x:v>骨与周围组织：胫骨内侧缘；邻近骨膜及筋膜
-邻近肌群：胫骨后肌；趾长屈肌；比目鱼肌</x:v>
+        <x:v>骨与周围组织：胫骨内侧缘；骨膜及筋膜
+邻近肌群：比目鱼肌；深层胫骨后肌、趾长屈肌
+远端邻近：内踝后方屈肌腱走行</x:v>
       </x:c>
       <x:c r="I31" s="144" t="str">
-        <x:v>baseline://clinical-extension/LocationGuide/LOC-LL-MEDIAL
-https://www.ncbi.nlm.nih.gov/books/NBK537340/
-https://www.ncbi.nlm.nih.gov/books/NBK539913/</x:v>
+        <x:v>https://anatomy.med.utah.edu/diganat/PT/2014_lecture/L11_leg_knee.pdf
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1751,8 +1816,16 @@
       <x:c r="G32" s="6" t="str">
         <x:v>与外踝/腓骨远端分开；神经或运动诱发胀痛等线索由Context/Safety继续分流</x:v>
       </x:c>
-      <x:c r="H32" s="144"/>
-      <x:c r="I32" s="144"/>
+      <x:c r="H32" s="144" t="str">
+        <x:v>肌肉：腓骨长肌；腓骨短肌
+前外侧邻近：第三腓骨肌；趾长伸肌
+骨与周围组织：腓骨；小腿外侧筋膜
+神经邻近：浅腓神经</x:v>
+      </x:c>
+      <x:c r="I32" s="144" t="str">
+        <x:v>https://anatomy.med.utah.edu/diganat/PT/2014_lecture/L11_leg_knee.pdf
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="6" t="str">
@@ -1776,8 +1849,16 @@
       <x:c r="G33" s="6" t="str">
         <x:v>区域名仅表示优先定位；需结合伸膝位/屈膝位、触诊和力量测试区分腓肠肌与其他组织</x:v>
       </x:c>
-      <x:c r="H33" s="144"/>
-      <x:c r="I33" s="144"/>
+      <x:c r="H33" s="144" t="str">
+        <x:v>表浅肌群：腓肠肌内侧头与外侧头
+深层邻近：比目鱼肌；跖肌
+近膝邻近：腘肌；腘绳肌远端；膝后关节囊
+骨与周围组织：胫骨、腓骨近端后方；后侧筋膜</x:v>
+      </x:c>
+      <x:c r="I33" s="144" t="str">
+        <x:v>https://anatomy.med.utah.edu/diganat/PT/2014_lecture/L11_leg_knee.pdf
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="6" t="str">
@@ -1801,8 +1882,15 @@
       <x:c r="G34" s="6" t="str">
         <x:v>与跟腱近端和腓肠肌上段分开；不能仅凭位置诊断比目鱼肌问题</x:v>
       </x:c>
-      <x:c r="H34" s="144"/>
-      <x:c r="I34" s="144"/>
+      <x:c r="H34" s="144" t="str">
+        <x:v>肌肉与肌腱：比目鱼肌；腓肠肌远端；跟腱近端
+深层邻近：胫骨后肌；趾长屈肌；拇长屈肌
+其他组织：跖肌腱；后侧筋膜</x:v>
+      </x:c>
+      <x:c r="I34" s="144" t="str">
+        <x:v>https://anatomy.med.utah.edu/diganat/PT/2014_lecture/L11_leg_knee.pdf
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="96" customHeight="1">
       <x:c r="A35" s="6" t="str">
@@ -1829,13 +1917,12 @@
       <x:c r="H35" s="144" t="str">
         <x:v>深层肌群：胫骨后肌；趾长屈肌；拇长屈肌
 表浅邻近：比目鱼肌；腓肠肌内侧头
-神经与血管：胫神经；胫后血管
-骨与周围组织：胫骨后内侧；邻近筋膜</x:v>
+骨与周围组织：胫骨后内侧；骨间膜及筋膜
+神经与血管：胫神经；胫后血管</x:v>
       </x:c>
       <x:c r="I35" s="144" t="str">
-        <x:v>baseline://clinical-extension/LocationGuide/LOC-LL-POSTMEDIAL
-https://www.ncbi.nlm.nih.gov/books/NBK537340/
-https://www.ncbi.nlm.nih.gov/books/NBK539913/</x:v>
+        <x:v>https://anatomy.med.utah.edu/diganat/PT/2014_lecture/L11_leg_knee.pdf
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1860,8 +1947,16 @@
       <x:c r="G36" s="6" t="str">
         <x:v>L3是症状定位，不等同股四头肌拉伤诊断；近端髋腹股沟问题不在本模块直接展开</x:v>
       </x:c>
-      <x:c r="H36" s="144"/>
-      <x:c r="I36" s="144"/>
+      <x:c r="H36" s="144" t="str">
+        <x:v>肌肉：股直肌；股内侧肌；股外侧肌
+深层邻近：股中间肌
+斜行经过：缝匠肌
+骨与周围组织：股骨；股四头肌筋膜；远端股四头肌腱</x:v>
+      </x:c>
+      <x:c r="I36" s="144" t="str">
+        <x:v>https://www.ncbi.nlm.nih.gov/books/NBK500008/
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="6" t="str">
@@ -1885,8 +1980,15 @@
       <x:c r="G37" s="6" t="str">
         <x:v>不把后侧疼痛自动等同腘绳肌拉伤；坐骨结节/骨盆近端问题属于后续髋骨盆模块边界</x:v>
       </x:c>
-      <x:c r="H37" s="144"/>
-      <x:c r="I37" s="144"/>
+      <x:c r="H37" s="144" t="str">
+        <x:v>肌肉：股二头肌长头与短头；半腱肌；半膜肌
+周围组织：腘绳肌腱膜及远端肌腱
+骨与深层邻近：股骨；坐骨神经</x:v>
+      </x:c>
+      <x:c r="I37" s="144" t="str">
+        <x:v>https://www.ncbi.nlm.nih.gov/books/NBK500008/
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="6" t="str">
@@ -1910,8 +2012,16 @@
       <x:c r="G38" s="6" t="str">
         <x:v>不把近腹股沟疼痛全部归入内收肌；明显腹股沟/耻骨/髋关节线索需按未来髋骨盆模块或医学评估处理</x:v>
       </x:c>
-      <x:c r="H38" s="144"/>
-      <x:c r="I38" s="144"/>
+      <x:c r="H38" s="144" t="str">
+        <x:v>肌肉：内收长肌；内收大肌；股薄肌
+深层邻近：内收短肌；耻骨肌
+斜行经过：缝匠肌
+骨与周围组织：股骨内侧；内收肌筋膜；远端鹅足肌腱</x:v>
+      </x:c>
+      <x:c r="I38" s="144" t="str">
+        <x:v>https://www.ncbi.nlm.nih.gov/books/NBK500008/
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="6" t="str">
@@ -1935,8 +2045,15 @@
       <x:c r="G39" s="6" t="str">
         <x:v>髂胫束本身不作为可孤立拉伸的肌肉；近端髋外侧问题不在本模块直接展开</x:v>
       </x:c>
-      <x:c r="H39" s="144"/>
-      <x:c r="I39" s="144"/>
+      <x:c r="H39" s="144" t="str">
+        <x:v>肌肉：股外侧肌；近端阔筋膜张肌
+筋膜与邻近肌群：髂胫束；后外侧股二头肌
+骨与远端邻近：股骨外侧；股骨外侧髁；膝外侧软组织</x:v>
+      </x:c>
+      <x:c r="I39" s="144" t="str">
+        <x:v>https://www.ncbi.nlm.nih.gov/books/NBK500008/
+BodyParts3D 4.0，当前原始模型组织与骨性标志核对；区域邻近关系，不作为组织诊断</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10978,7 +11095,7 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="M26" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N26" s="113"/>
       <x:c r="O26" s="113"/>
@@ -11021,7 +11138,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="M27" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N27" s="113"/>
       <x:c r="O27" s="113"/>
@@ -11451,7 +11568,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="M37" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N37" s="113"/>
       <x:c r="O37" s="113"/>
@@ -11537,7 +11654,7 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="M39" s="113" t="str">
-        <x:v>DEFAULT</x:v>
+        <x:v>EXPAND</x:v>
       </x:c>
       <x:c r="N39" s="113"/>
       <x:c r="O39" s="113"/>
@@ -11838,7 +11955,7 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="M46" s="113" t="str">
-        <x:v>DEFAULT</x:v>
+        <x:v>EXPAND</x:v>
       </x:c>
       <x:c r="N46" s="113"/>
       <x:c r="O46" s="113"/>
@@ -12053,7 +12170,7 @@
         <x:v>1006</x:v>
       </x:c>
       <x:c r="M51" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N51" s="113"/>
       <x:c r="O51" s="113"/>
@@ -12225,7 +12342,7 @@
         <x:v>1005</x:v>
       </x:c>
       <x:c r="M55" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N55" s="113"/>
       <x:c r="O55" s="113"/>
@@ -12354,7 +12471,7 @@
         <x:v>1006</x:v>
       </x:c>
       <x:c r="M58" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N58" s="113"/>
       <x:c r="O58" s="113"/>
@@ -12655,7 +12772,7 @@
         <x:v>5002</x:v>
       </x:c>
       <x:c r="M65" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N65" s="113"/>
       <x:c r="O65" s="113"/>
@@ -14676,7 +14793,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="M112" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N112" s="113"/>
       <x:c r="O112" s="113"/>
@@ -15450,7 +15567,7 @@
         <x:v>3002</x:v>
       </x:c>
       <x:c r="M130" s="113" t="str">
-        <x:v>LINKED</x:v>
+        <x:v>EXPAND</x:v>
       </x:c>
       <x:c r="N130" s="113"/>
       <x:c r="O130" s="113"/>
@@ -15794,7 +15911,7 @@
         <x:v>3001</x:v>
       </x:c>
       <x:c r="M138" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N138" s="113"/>
       <x:c r="O138" s="113"/>
@@ -16267,7 +16384,7 @@
         <x:v>6001</x:v>
       </x:c>
       <x:c r="M149" s="113" t="str">
-        <x:v>LINKED</x:v>
+        <x:v>EXPAND</x:v>
       </x:c>
       <x:c r="N149" s="113"/>
       <x:c r="O149" s="113"/>
@@ -16310,7 +16427,7 @@
         <x:v>6001</x:v>
       </x:c>
       <x:c r="M150" s="113" t="str">
-        <x:v>LINKED</x:v>
+        <x:v>EXPAND</x:v>
       </x:c>
       <x:c r="N150" s="113"/>
       <x:c r="O150" s="113"/>
@@ -16439,7 +16556,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="M153" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N153" s="113"/>
       <x:c r="O153" s="113"/>
@@ -16482,7 +16599,7 @@
         <x:v>1003</x:v>
       </x:c>
       <x:c r="M154" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N154" s="113"/>
       <x:c r="O154" s="113"/>
@@ -16525,7 +16642,7 @@
         <x:v>1004</x:v>
       </x:c>
       <x:c r="M155" s="113" t="str">
-        <x:v>LINKED</x:v>
+        <x:v>EXPAND</x:v>
       </x:c>
       <x:c r="N155" s="113"/>
       <x:c r="O155" s="113"/>
@@ -16611,7 +16728,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="M157" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N157" s="113"/>
       <x:c r="O157" s="113"/>
@@ -16654,7 +16771,7 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="M158" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N158" s="113"/>
       <x:c r="O158" s="113"/>
@@ -16740,7 +16857,7 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="M160" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N160" s="113"/>
       <x:c r="O160" s="113"/>
@@ -16783,7 +16900,7 @@
         <x:v>3001</x:v>
       </x:c>
       <x:c r="M161" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N161" s="113"/>
       <x:c r="O161" s="113"/>
@@ -16826,7 +16943,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="M162" s="113" t="str">
-        <x:v>LINKED</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N162" s="113"/>
       <x:c r="O162" s="113"/>
@@ -17299,7 +17416,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="M173" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N173" s="113"/>
       <x:c r="O173" s="113"/>
@@ -17342,7 +17459,7 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="M174" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N174" s="113"/>
       <x:c r="O174" s="113"/>
@@ -17471,7 +17588,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="M177" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N177" s="113"/>
       <x:c r="O177" s="113"/>
@@ -17600,7 +17717,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="M180" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N180" s="113"/>
       <x:c r="O180" s="113"/>
@@ -17729,7 +17846,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="M183" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N183" s="113"/>
       <x:c r="O183" s="113"/>
@@ -17815,7 +17932,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="M185" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N185" s="113"/>
       <x:c r="O185" s="113"/>
@@ -27576,7 +27693,7 @@
         <x:v>1003</x:v>
       </x:c>
       <x:c r="M412" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N412" s="113"/>
       <x:c r="O412" s="113"/>
@@ -27748,7 +27865,7 @@
         <x:v>1005</x:v>
       </x:c>
       <x:c r="M416" s="113" t="str">
-        <x:v>LINKED</x:v>
+        <x:v>EXPAND</x:v>
       </x:c>
       <x:c r="N416" s="113"/>
       <x:c r="O416" s="113"/>
@@ -28178,7 +28295,7 @@
         <x:v>1004</x:v>
       </x:c>
       <x:c r="M426" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N426" s="113"/>
       <x:c r="O426" s="113"/>
@@ -28264,7 +28381,7 @@
         <x:v>1005</x:v>
       </x:c>
       <x:c r="M428" s="113" t="str">
-        <x:v>LINKED</x:v>
+        <x:v>EXPAND</x:v>
       </x:c>
       <x:c r="N428" s="113"/>
       <x:c r="O428" s="113"/>
@@ -28393,7 +28510,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="M431" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N431" s="113"/>
       <x:c r="O431" s="113"/>
@@ -28479,7 +28596,7 @@
         <x:v>3001</x:v>
       </x:c>
       <x:c r="M433" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N433" s="113"/>
       <x:c r="O433" s="113"/>
@@ -28565,7 +28682,7 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="M435" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N435" s="113"/>
       <x:c r="O435" s="113"/>
@@ -28608,7 +28725,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="M436" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N436" s="113"/>
       <x:c r="O436" s="113"/>
@@ -28823,7 +28940,7 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="M441" s="113" t="str">
-        <x:v>EXPAND</x:v>
+        <x:v>DEFAULT</x:v>
       </x:c>
       <x:c r="N441" s="113"/>
       <x:c r="O441" s="113"/>
@@ -32822,7 +32939,7 @@
         <x:v>9002</x:v>
       </x:c>
       <x:c r="M534" t="str">
-        <x:v>LINKED</x:v>
+        <x:v>EXPAND</x:v>
       </x:c>
       <x:c r="N534"/>
       <x:c r="O534"/>
@@ -32908,7 +33025,7 @@
         <x:v>9002</x:v>
       </x:c>
       <x:c r="M536" t="str">
-        <x:v>LINKED</x:v>
+        <x:v>EXPAND</x:v>
       </x:c>
       <x:c r="N536"/>
       <x:c r="O536"/>
@@ -34589,6 +34706,49 @@
       </x:c>
       <x:c r="N575" s="112"/>
       <x:c r="O575" s="112"/>
+    </x:row>
+    <x:row r="576" ht="210" customHeight="1">
+      <x:c r="A576" t="str">
+        <x:v>RCM-COMMON-KNEE-PL</x:v>
+      </x:c>
+      <x:c r="B576" t="str">
+        <x:v>KNEE-R-011</x:v>
+      </x:c>
+      <x:c r="C576" t="str">
+        <x:v>CORE-MUS-PL</x:v>
+      </x:c>
+      <x:c r="D576" t="str">
+        <x:v>肌肉状态</x:v>
+      </x:c>
+      <x:c r="E576" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F576" t="str">
+        <x:v>Default</x:v>
+      </x:c>
+      <x:c r="G576" t="str">
+        <x:v>Stable</x:v>
+      </x:c>
+      <x:c r="H576" t="str">
+        <x:v>Lower Leg Remaining L3 Review v2.6</x:v>
+      </x:c>
+      <x:c r="I576" t="str">
+        <x:v>局部直接相关</x:v>
+      </x:c>
+      <x:c r="J576" t="str">
+        <x:v>MUSCLE_STATE</x:v>
+      </x:c>
+      <x:c r="K576" t="str">
+        <x:v>膝外侧邻近肌群</x:v>
+      </x:c>
+      <x:c r="L576" t="n">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="M576" t="str">
+        <x:v>DEFAULT</x:v>
+      </x:c>
+      <x:c r="N576"/>
+      <x:c r="O576"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
